--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_10_Data Pipeline _ Observability/Day_10_Phan_01_22_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/01_CHUAN_IMPORT_QUIZIZZ_QUIZ_COM_904_CAU/Day_10_Data Pipeline _ Observability/Day_10_Phan_01_22_Cau.xlsx
@@ -1350,7 +1350,7 @@
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3</t>
         </is>
       </c>
       <c r="I18" s="4" t="n">
@@ -1359,7 +1359,7 @@
       <c r="J18" s="3" t="n"/>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Assume lần đầu có thể đã ghi một phần, nên replay phải không nhân bản.</t>
+          <t>Khi trang P7 bị timeout sau khi server có thể đã xử lý nhưng client chưa nhận được phản hồi xác nhận: (a) Lưu lại định danh/cursor của P7 kèm số lần thử và thông tin lỗi; (b) Giữ nguyên checkpoint tại trang thành công trước đó (P6); (c) Khi thực hiện replay trang P7 phải sử dụng mã định danh ổn định của từng bản ghi để đảm bảo tính idempotent (không nhân bản dữ liệu nếu server đã ghi một phần). Không được nhảy cóc sang P8.</t>
         </is>
       </c>
     </row>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1,2,3,5</t>
         </is>
       </c>
       <c r="I20" s="4" t="n">
@@ -1456,7 +1456,7 @@
       <c r="J20" s="3" t="n"/>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: OCR quality không chỉ là một scalar confidence.</t>
+          <t>Các dấu hiệu cảnh báo chất lượng OCR kém cần cách ly (quarantine) để người xem xét trước khi đưa vào embedding: (a) Điểm độ tin cậy thấp (0,42) và xuất hiện nhiều ký tự thay thế lỗi; (b) Ngôn ngữ văn bản bị thay đổi bất thường (từ tiếng Việt sang tiếng Nga); (c) Chiều dài văn bản giảm đột ngột 95% so với các trang tương tự; (e) Bảng dữ liệu bị mất các cột dù số lượng từ ngữ vẫn đủ.</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1800</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
@@ -1501,7 +1501,7 @@
       <c r="J21" s="3" t="n"/>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Tính chênh rate rồi nhân thời gian.</t>
+          <t>Tốc độ chênh lệch giữa producer và consumer là: 120 event/s - 90 event/s = 30 event/s. Trong khoảng thời gian 60 giây không co giãn (no scaling), độ sâu hàng đợi (queue depth) tăng thêm là: 30 event/s × 60 s = 1800 event.</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>o1 → o2 → o3 → o4 → o5</t>
+          <t>o2 → o3 → o4 → o5 → o1</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
@@ -1598,7 +1598,7 @@
       <c r="J23" s="3" t="n"/>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>Phân tích theo nguyên lý thiết kế: Không replay trước khi biết nguyên nhân vẫn tồn tại.</t>
+          <t>Trình tự xử lý thông điệp độc hại (poison message workflow) với Dead-Letter Queue (DLQ): 1. Consumer tiếp nhận và xử lý message (o2) -&gt; 2. Thử lại có giới hạn (bounded retries) theo điều kiện eligibility (o3) -&gt; 3. Đưa failed event kèm lý do vi phạm và run ID vào DLQ để không chặn nghẽn hàng đợi (o4) -&gt; 4. Kỹ sư kiểm tra, tạo ticket và khắc phục nguyên nhân gốc (o5) -&gt; 5. Replay có chủ đích các message trong DLQ sau khi đã sửa lỗi (o1).</t>
         </is>
       </c>
     </row>
